--- a/regression_deneme/regression_with_nn/anadolu caddesi_weekly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/anadolu caddesi_weekly_true_and_predicted_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         <v>2025</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38872233534099</v>
+        <v>1.866631356763028</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2025</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13.63340544647399</v>
+        <v>10.95482351224872</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>2025</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>13.09537542899754</v>
+        <v>13.27382236358051</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>2025</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>19.48549691993639</v>
+        <v>13.06225979233376</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>9.720580179408355</v>
+        <v>15.88273809114839</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>2025</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>11.15091583948607</v>
+        <v>15.11743936181806</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>14.50211625274789</v>
+        <v>13.32731039069072</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>2025</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>15.38616428520259</v>
+        <v>12.90664336310307</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>2025</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>6.096606806248555</v>
+        <v>13.63927425627966</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>2025</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>10.6059135348544</v>
+        <v>11.5856254764982</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>2025</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>16.09599702290991</v>
+        <v>10.64139243421772</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>2025</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>14.21256724274766</v>
+        <v>13.88739758917812</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>2025</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>12.80823510701035</v>
+        <v>16.90160108489016</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>2025</v>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>13.90318790358126</v>
+        <v>13.47412697480156</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>2025</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>17.16222754941571</v>
+        <v>15.08123624998315</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>2025</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86687278353379</v>
+        <v>14.34483357477692</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>2025</v>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>12.13859117118874</v>
+        <v>15.18600550428992</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>2025</v>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>10.06431096676773</v>
+        <v>12.50021617075316</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>2025</v>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>7.55833875775453</v>
+        <v>11.01046189550378</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>2025</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>10.19211566620391</v>
+        <v>9.806713817426557</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>2025</v>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>13.06474912051815</v>
+        <v>11.28231491842215</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>2025</v>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>16.44152062002156</v>
+        <v>13.3354024205235</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>2025</v>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>11.13280993618814</v>
+        <v>16.15505770308675</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>2025</v>
       </c>
       <c r="B25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>9.082330056009777</v>
+        <v>13.88894239649163</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>2025</v>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>10.63333724386214</v>
+        <v>10.64473713878106</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>8.757280472254829</v>
+        <v>11.40521134630983</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>2025</v>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>12.55733849039695</v>
+        <v>11.23148195152316</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>2025</v>
       </c>
       <c r="B29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>13.16682656039953</v>
+        <v>11.10044273999288</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>2025</v>
       </c>
       <c r="B30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>12.9189484658034</v>
+        <v>13.13404778371206</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,27 @@
         <v>2025</v>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
         <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>10.96197852147212</v>
+        <v>13.82510845666373</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B32" t="n">
+        <v>35</v>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11.84603271293226</v>
       </c>
     </row>
   </sheetData>
